--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.8046582404949</v>
+        <v>3.543256964080421</v>
       </c>
       <c r="D2" t="n">
-        <v>21.73709288750848</v>
+        <v>3.532277594220128</v>
       </c>
       <c r="E2" t="n">
-        <v>8.910494883138872</v>
+        <v>1.447955418510067</v>
       </c>
       <c r="F2" t="n">
-        <v>8.281385301154545</v>
+        <v>1.345725111437614</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.983668474217154</v>
+        <v>0.6473461270602875</v>
       </c>
       <c r="D3" t="n">
-        <v>5.174322285199392</v>
+        <v>0.8408273713449013</v>
       </c>
       <c r="E3" t="n">
-        <v>8.910494883138872</v>
+        <v>1.447955418510067</v>
       </c>
       <c r="F3" t="n">
-        <v>8.281385301154545</v>
+        <v>1.345725111437614</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
